--- a/sample_asset_ledger.xlsx
+++ b/sample_asset_ledger.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="고정자산대장" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'고정자산대장'!$A$1:$K$14</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,23 +28,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -60,13 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,83 +417,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:T110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>자산명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>자산분류(유형자산/무형자산)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>취득일</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>취득원가</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>잔존가치</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>내용연수(년)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>상각방법(정액법/정률법)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>회사반영_당기감가상각비</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>처분일</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>내용연수재추정일</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>재추정후내용연수(년)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>재추정후상각방법(정액법/정률법)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>총예정생산량</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>당기실제생산량</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>전기말누적생산량</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>자본적지출일</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>자본적지출액</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>상각중단시작일</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>상각중단종료일</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>회사반영_전기말감가상각누계액</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>본사건물</t>
+          <t>정액법기본자산_유형01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -516,31 +533,45 @@
           <t>유형자산</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>43539</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>50000000</v>
+      <c r="C2" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>정액법</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>15000000</v>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>10500000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>생산설비A</t>
+          <t>정액법기본자산_유형02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,31 +579,45 @@
           <t>유형자산</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>44013</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="E3" s="3" t="n">
+      <c r="C3" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>정액법</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
-        <v>12500000</v>
+      <c r="H3" t="n">
+        <v>1833333</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>4736110</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>차량운반구</t>
+          <t>정액법기본자산_유형03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -580,31 +625,45 @@
           <t>유형자산</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>45026</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>5000000</v>
+      <c r="C4" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>정액법</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>8000000</v>
+      <c r="H4" t="n">
+        <v>1437500</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>2156250</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>사무집기비품</t>
+          <t>정액법기본자산_유형04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -612,95 +671,137 @@
           <t>유형자산</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="C5" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>정액법</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>1200000</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>소프트웨어라이선스</t>
+          <t>정액법기본자산_유형05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>무형자산</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>45292</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="E6" s="3" t="n">
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>44270</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>정액법</t>
         </is>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>6000000</v>
+      <c r="H6" t="n">
+        <v>520833</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>11979167</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>상표권</t>
+          <t>정액법기본자산_유형06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>무형자산</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>44336</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="E7" s="3" t="n">
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>정액법</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>1800000</v>
+      <c r="H7" t="n">
+        <v>1857143</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>11142858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>인테리어시설</t>
+          <t>정액법기본자산_유형07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -708,31 +809,45 @@
           <t>유형자산</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>45717</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="E8" s="3" t="n">
+      <c r="C8" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>정액법</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n">
-        <v>5000000</v>
+      <c r="H8" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>기계장치B</t>
+          <t>정액법기본자산_유형08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -740,168 +855,229 @@
           <t>유형자산</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>44562</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>80000000</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>4000000</v>
+      <c r="C9" s="1" t="n">
+        <v>43221</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>정률법</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>5970127</v>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1166667</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>7777780</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>기계장치C</t>
+          <t>정액법기본자산_무형01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유형자산</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>45200</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>3000000</v>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8300000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>정률법</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>12500000</v>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>8300000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>냉동설비</t>
+          <t>정액법기본자산_무형02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유형자산</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>44428</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>2000000</v>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>정률법</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>2931526</v>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>860000</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>2221667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>복사기</t>
+          <t>정액법기본자산_무형03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>유형자산</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>44228</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="E12" s="3" t="n">
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>정액법</t>
         </is>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>600000</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>45838</v>
+      <c r="H12" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>3337500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>특수기계</t>
+          <t>정액법기본자산_무형04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>유형자산</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>44197</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="E13" s="3" t="n">
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>정액법</t>
         </is>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>6666667</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>45292</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
+      <c r="H13" t="n">
+        <v>1314286</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>109524</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>노후설비</t>
+          <t>정률법기본자산_유형01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -909,29 +1085,4836 @@
           <t>유형자산</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>42005</v>
-      </c>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12400000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>12400001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>정률법기본자산_유형02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="D15" t="n">
+        <v>12800000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1426383</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>9179739</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>정률법기본자산_유형03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13200000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2394198</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>5550805</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>정률법기본자산_유형04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>3446375</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>293533</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>정률법기본자산_유형05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>44270</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1183112</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>7499384</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>정률법기본자산_유형06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>14400000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>정률법기본자산_유형07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="D20" t="n">
+        <v>14800000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2072000</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>정률법기본자산_유형08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>43221</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15200000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>773480</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>8355046</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>정률법기본자산_무형01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9350000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>9350001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>정률법기본자산_무형02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1178300</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>5551058</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>정률법기본자산_무형03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10050000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1539011</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>3086149</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>정률법기본자산_무형04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10400000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>22</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1317001</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>110933</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>생산량비례법기본자산_유형01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D26" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>생산량비례법</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1620000</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N26" t="n">
+        <v>9000</v>
+      </c>
+      <c r="O26" t="n">
+        <v>42000</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>생산량비례법기본자산_유형02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D27" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>생산량비례법</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O27" t="n">
+        <v>44000</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>생산량비례법기본자산_유형03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D28" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>생산량비례법</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1980000</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N28" t="n">
+        <v>11000</v>
+      </c>
+      <c r="O28" t="n">
+        <v>46000</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>생산량비례법기본자산_유형04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D29" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>생산량비례법</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>생산량비례법기본자산_무형01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="D30" t="n">
         <v>15000000</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>생산량비례법</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>50000</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6500</v>
+      </c>
+      <c r="O30" t="n">
+        <v>21000</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>생산량비례법기본자산_무형02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="D31" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>생산량비례법</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>50000</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7000</v>
+      </c>
+      <c r="O31" t="n">
+        <v>22000</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>처분_정액_당기중_유형01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>처분_정액_당기중_무형01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>처분_정액_전기이전_유형01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>처분_정률_당기중_유형01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
         <v>8</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>정액법</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>348611</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>11658678</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>처분_정률_당기중_무형01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>884134</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>8552005</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>처분_정률_전기이전_유형01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>43101</v>
+      </c>
+      <c r="D37" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>45291</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>처분_정액_당기중_유형02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>416667</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>2216667</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>처분_정률_당기중_유형02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>617191</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>12425535</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>처분_정액_전기이전_무형01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>43101</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>처분_정률_전기이전_무형01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>42736</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>9999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>재추정_정액_유형01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D42" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K42" t="n">
+        <v>8</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>8600000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>재추정_정액_무형01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D43" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>562500</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="K43" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="n">
+        <v>5906250</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>재추정_정률_유형01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D44" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>597949</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K44" t="n">
+        <v>10</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>12041318</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>재추정_정률_무형01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>648106</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K45" t="n">
+        <v>8</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="n">
+        <v>7929375</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>재추정_정액_유형02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D46" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>428571</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="K46" t="n">
+        <v>7</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>7857142</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>재추정_정률_유형02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D47" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>313188</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="K47" t="n">
+        <v>9</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="n">
+        <v>11897226</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>방법변경_정액to정률_01</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D48" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>2005618</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="n">
+        <v>6909600</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>방법변경_정액to정률_02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D49" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1327711</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="K49" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="n">
+        <v>5625000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>방법변경_정률to정액_01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>753725</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="n">
+        <v>11231376</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>방법변경_정률to정액_02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D51" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>983478</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="n">
+        <v>7772453</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>자본적지출_정액_전기_01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D52" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1285714</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="n">
+        <v>5121428</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>자본적지출_정액_당기초_01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="D53" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>자본적지출_정액_당기중_01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D54" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1868421</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>자본적지출_정액_당기말_01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D55" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1461538</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>800000</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="n">
+        <v>4200000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>자본적지출_정률_전기_01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D56" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1165593</v>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="n">
+        <v>11999641</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>자본적지출_정률_당기초_01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="D57" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>8</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>925374</v>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="n">
+        <v>9843534</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>자본적지출_정률_당기중_01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D58" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>9</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1252484</v>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="n">
+        <v>8846206</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>자본적지출_정률_당기말_01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D59" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>846503</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>900000</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="n">
+        <v>7385822</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>상각중단_정액_당기전체_01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="S60" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="T60" t="n">
+        <v>6600000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>상각중단_정률_당기전체_01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D61" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="S61" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="T61" t="n">
+        <v>9182734</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>상각중단_정액_당기일부_01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D62" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>700000</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="S62" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5300000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>상각중단_정률_당기일부_01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D63" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>545427</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="S63" s="1" t="n">
+        <v>45199</v>
+      </c>
+      <c r="T63" t="n">
+        <v>7790627</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>상각중단_정액_재개후_01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="S64" s="1" t="n">
+        <v>44377</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5400000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>상각중단_정률_재개후_01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D65" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>462386</v>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="S65" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="T65" t="n">
+        <v>6974753</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>상각중단_정액_당기일부_02</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D66" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="S66" s="1" t="n">
+        <v>45596</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3625000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>상각중단_정률_재개후_02</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>180274</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="S67" s="1" t="n">
+        <v>44651</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4987859</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>추가취득_정액_01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>583333</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>추가취득_정액_02</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>추가취득_정액_03</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>추가취득_정액_04</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>83333</v>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>추가취득_정률_01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>6</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1379000</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>추가취득_정률_02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="D73" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>6</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1182000</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>추가취득_정률_03</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="D74" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>2364000</v>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>추가취득_정률_04</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>197000</v>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>조합_capex먼저reest나중</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D76" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>8</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1082176</v>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="K76" t="n">
+        <v>6</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="n">
+        <v>5138214</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>조합_reest먼저capex나중</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D77" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1468182</v>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="K77" t="n">
+        <v>6</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="n">
+        <v>5127273</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>조합_capex중단_01</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D78" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>6</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="R78" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="S78" s="1" t="n">
+        <v>45535</v>
+      </c>
+      <c r="T78" t="n">
+        <v>5812500</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>조합_capex중단_02</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D79" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>6</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>852241</v>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="R79" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="S79" s="1" t="n">
+        <v>45412</v>
+      </c>
+      <c r="T79" t="n">
+        <v>7536952</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>조합_reest중단_01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D80" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>7</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1309524</v>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="K80" t="n">
+        <v>6</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="S80" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4998017</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>조합_reest중단_02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D81" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>7</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>608804</v>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="K81" t="n">
+        <v>6</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="S81" s="1" t="n">
+        <v>45443</v>
+      </c>
+      <c r="T81" t="n">
+        <v>10454812</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>조합_처분capex_01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D82" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>5</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="n">
+        <v>5133333</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>조합_처분capex_02</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D83" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>6</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>318691</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="n">
+        <v>8482280</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>조합_처분중단_01</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D84" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>5</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1166667</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="S84" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4900000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>조합_처분중단_02</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D85" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>6</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>201938</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="S85" s="1" t="n">
+        <v>44804</v>
+      </c>
+      <c r="T85" t="n">
+        <v>9269920</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>조합_처분reest_01</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D86" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>6</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>844444</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>45900</v>
+      </c>
+      <c r="J86" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="K86" t="n">
+        <v>5</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="n">
+        <v>5700000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>조합_처분reest_02</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D87" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>7</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>290927</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="J87" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="K87" t="n">
+        <v>5</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="n">
+        <v>10693552</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>3조합_capex_reest_중단_01</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D88" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>8</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>555556</v>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K88" t="n">
+        <v>6</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R88" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="S88" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="T88" t="n">
+        <v>7444445</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3조합_capex_reest_중단_02</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D89" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>8</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>431435</v>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K89" t="n">
+        <v>6</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="R89" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="S89" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="T89" t="n">
+        <v>11909974</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>3조합_capex_reest_처분_01</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D90" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>8</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>885417</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="J90" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="K90" t="n">
+        <v>6</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="n">
+        <v>5577779</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>3조합_capex_reest_처분_02</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="D91" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>9</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>328975</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="J91" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="K91" t="n">
+        <v>7</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="n">
+        <v>13614758</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3조합_capex_중단_처분_01</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D92" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>6</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1416667</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>800000</v>
+      </c>
+      <c r="R92" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="S92" s="1" t="n">
+        <v>45473</v>
+      </c>
+      <c r="T92" t="n">
+        <v>5550000</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3조합_capex_중단_처분_02</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D93" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>6</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>490934</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>900000</v>
+      </c>
+      <c r="R93" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="S93" s="1" t="n">
+        <v>45443</v>
+      </c>
+      <c r="T93" t="n">
+        <v>7563957</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>3조합_reest_중단_처분_01</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D94" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>7</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>1200397</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="J94" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="K94" t="n">
+        <v>6</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="S94" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="T94" t="n">
+        <v>6416668</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3조합_reest_중단_처분_02</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="D95" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>7</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>933818</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="J95" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="K95" t="n">
+        <v>6</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="S95" s="1" t="n">
+        <v>45046</v>
+      </c>
+      <c r="T95" t="n">
+        <v>11566183</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>경계_capex reest동일날짜</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D96" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>5</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K96" t="n">
+        <v>4</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>경계_reest가중단구간안</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D97" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>6</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="K97" t="n">
+        <v>5</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="S97" s="1" t="n">
+        <v>45199</v>
+      </c>
+      <c r="T97" t="n">
+        <v>4687500</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>경계_처분이중단구간안</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D98" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>5</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>266667</v>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="S98" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="T98" t="n">
+        <v>4800000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>경계_capex직후방법변경</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D99" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>10</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>2211469</v>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="K99" t="n">
+        <v>5</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="n">
+        <v>3125000</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>경계_중단이중간구간</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D100" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>5</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="K100" t="n">
+        <v>3</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="S100" s="1" t="n">
+        <v>44561</v>
+      </c>
+      <c r="T100" t="n">
+        <v>5999999</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>경계_중단후재개후처분</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D101" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>8</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="S101" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="T101" t="n">
+        <v>6750000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>오류_내용연수0</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D102" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>오류_내용연수음수</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D103" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>오류_취득원가0이하</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>오류_잔존가치초과</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D105" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E105" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F105" t="n">
+        <v>5</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>오류_생산량비례법생산량누락</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D106" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>5</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>생산량비례법</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>오류_자본적지출날짜금액불일치</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D107" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>오류_상각중단시작종료역전</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D108" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="S108" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="T108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>오류_재추정후상각방법오타</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D109" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>5</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K109" t="n">
+        <v>4</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>정율법</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>오류_상각중단짝안맞음</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D110" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>5</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sample_asset_ledger.xlsx
+++ b/sample_asset_ledger.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T110"/>
+  <dimension ref="A1:T134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5503,7 +5503,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>오류_내용연수0</t>
+          <t>이중체감법기본자산_유형01</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5512,24 +5512,24 @@
         </is>
       </c>
       <c r="C102" s="1" t="n">
-        <v>44562</v>
+        <v>43831</v>
       </c>
       <c r="D102" t="n">
-        <v>10000000</v>
+        <v>11400000</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>정액법</t>
+          <t>이중체감법</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
@@ -5542,12 +5542,14 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
+      <c r="T102" t="n">
+        <v>10513536</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>오류_내용연수음수</t>
+          <t>이중체감법기본자산_유형02</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5556,24 +5558,24 @@
         </is>
       </c>
       <c r="C103" s="1" t="n">
-        <v>44562</v>
+        <v>44742</v>
       </c>
       <c r="D103" t="n">
-        <v>10000000</v>
+        <v>11800000</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F103" t="n">
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>정액법</t>
+          <t>이중체감법</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1000000</v>
+        <v>1417383</v>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
@@ -5586,12 +5588,14 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
+      <c r="T103" t="n">
+        <v>6130469</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>오류_취득원가0이하</t>
+          <t>이중체감법기본자산_유형03</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5600,24 +5604,24 @@
         </is>
       </c>
       <c r="C104" s="1" t="n">
-        <v>44562</v>
+        <v>45108</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>12200000</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>정액법</t>
+          <t>이중체감법</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>500000</v>
+        <v>1756800</v>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
@@ -5630,38 +5634,40 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
+      <c r="T104" t="n">
+        <v>3416000</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>오류_잔존가치초과</t>
+          <t>이중체감법기본자산_무형01</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>유형자산</t>
+          <t>무형자산</t>
         </is>
       </c>
       <c r="C105" s="1" t="n">
-        <v>44562</v>
+        <v>43831</v>
       </c>
       <c r="D105" t="n">
-        <v>10000000</v>
+        <v>8800000</v>
       </c>
       <c r="E105" t="n">
-        <v>15000000</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>정액법</t>
+          <t>이중체감법</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>500000</v>
+        <v>386283</v>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
@@ -5674,58 +5680,60 @@
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
+      <c r="T105" t="n">
+        <v>7641153</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>오류_생산량비례법생산량누락</t>
+          <t>이중체감법기본자산_무형02</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>유형자산</t>
+          <t>무형자산</t>
         </is>
       </c>
       <c r="C106" s="1" t="n">
-        <v>44562</v>
+        <v>44742</v>
       </c>
       <c r="D106" t="n">
-        <v>10000000</v>
+        <v>9100000</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>생산량비례법</t>
+          <t>이중체감법</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>500000</v>
+        <v>950842</v>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="n">
-        <v>5000</v>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
+      <c r="T106" t="n">
+        <v>3394946</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>오류_자본적지출날짜금액불일치</t>
+          <t>연수합계법기본자산_유형01</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5734,24 +5742,24 @@
         </is>
       </c>
       <c r="C107" s="1" t="n">
-        <v>44562</v>
+        <v>43831</v>
       </c>
       <c r="D107" t="n">
-        <v>10000000</v>
+        <v>10900000</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F107" t="n">
         <v>5</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>정액법</t>
+          <t>연수합계법</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
@@ -5760,18 +5768,18 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" s="1" t="n">
-        <v>45292</v>
-      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
+      <c r="T107" t="n">
+        <v>10400000</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>오류_상각중단시작종료역전</t>
+          <t>연수합계법기본자산_유형02</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5780,24 +5788,24 @@
         </is>
       </c>
       <c r="C108" s="1" t="n">
-        <v>44562</v>
+        <v>44742</v>
       </c>
       <c r="D108" t="n">
-        <v>10000000</v>
+        <v>11300000</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F108" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>정액법</t>
+          <t>연수합계법</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>500000</v>
+        <v>1542857</v>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
@@ -5808,18 +5816,16 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
-      <c r="R108" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="S108" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="T108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="n">
+        <v>5817857</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>오류_재추정후상각방법오타</t>
+          <t>연수합계법기본자산_유형03</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5828,37 +5834,29 @@
         </is>
       </c>
       <c r="C109" s="1" t="n">
-        <v>44562</v>
+        <v>45108</v>
       </c>
       <c r="D109" t="n">
-        <v>10000000</v>
+        <v>11700000</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>정액법</t>
+          <t>연수합계법</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>500000</v>
+        <v>1629091</v>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="K109" t="n">
-        <v>4</v>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>정율법</t>
-        </is>
-      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
@@ -5866,38 +5864,40 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
+      <c r="T109" t="n">
+        <v>2850909</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>오류_상각중단짝안맞음</t>
+          <t>연수합계법기본자산_무형01</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>유형자산</t>
+          <t>무형자산</t>
         </is>
       </c>
       <c r="C110" s="1" t="n">
-        <v>44562</v>
+        <v>43831</v>
       </c>
       <c r="D110" t="n">
-        <v>10000000</v>
+        <v>8500000</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>정액법</t>
+          <t>연수합계법</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
@@ -5908,11 +5908,1171 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
-      <c r="R110" s="1" t="n">
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="n">
+        <v>8500000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>연수합계법기본자산_무형02</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>9</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>연수합계법</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>1173333</v>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="n">
+        <v>3960000</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>처분_이중체감_당기중_유형01</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D112" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>이중체감법</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>460905</v>
+      </c>
+      <c r="I112" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="n">
+        <v>9629630</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>처분_연수합계_당기중_유형01</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D113" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>6</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>연수합계법</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>529206</v>
+      </c>
+      <c r="I113" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="n">
+        <v>9428572</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>재추정_이중체감_유형01</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D114" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>6</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>이중체감법</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>722222</v>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" s="1" t="n">
         <v>45292</v>
       </c>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
+      <c r="K114" t="n">
+        <v>8</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="n">
+        <v>10111111</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>재추정_연수합계_유형01</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D115" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>6</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>연수합계법</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>694444</v>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K115" t="n">
+        <v>8</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="n">
+        <v>10122222</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>방법변경_정액to이중체감_01</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D116" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>8</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>1666667</v>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K116" t="n">
+        <v>6</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>이중체감법</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="n">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>방법변경_정률to연수합계_01</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D117" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>8</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>715997</v>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K117" t="n">
+        <v>6</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>연수합계법</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="n">
+        <v>11352009</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>방법변경_이중체감to정액_01</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D118" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>8</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>이중체감법</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>606445</v>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K118" t="n">
+        <v>6</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="n">
+        <v>8467774</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>방법변경_연수합계to정률_01</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D119" t="n">
+        <v>12800000</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>8</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>연수합계법</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>1402442</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="K119" t="n">
+        <v>5</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>정률법</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="n">
+        <v>9357777</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>자본적지출_이중체감_전기_01</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D120" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>10</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>이중체감법</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>1042432</v>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="n">
+        <v>8787840</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>자본적지출_연수합계_전기_01</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D121" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>10</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>연수합계법</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>695868</v>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="n">
+        <v>7454710</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>상각중단_이중체감_당기일부_01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D122" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>5</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>이중체감법</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>205200</v>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="S122" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="T122" t="n">
+        <v>8268800</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>상각중단_연수합계_당기일부_01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="D123" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>연수합계법</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>272222</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="S123" s="1" t="n">
+        <v>45900</v>
+      </c>
+      <c r="T123" t="n">
+        <v>9146667</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>오류_내용연수0</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D124" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>오류_내용연수음수</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D125" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>오류_취득원가0이하</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>5</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>오류_잔존가치초과</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D127" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E127" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F127" t="n">
+        <v>5</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>오류_생산량비례법생산량누락</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D128" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>5</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>생산량비례법</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>오류_자본적지출날짜금액불일치</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D129" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>5</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>오류_상각중단시작종료역전</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D130" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>5</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="S130" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="T130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>오류_재추정후상각방법오타</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D131" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>5</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="K131" t="n">
+        <v>4</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>정율법</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>오류_상각중단짝안맞음</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D132" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>5</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>정액법</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>오류_이중체감_내용연수0</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D133" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>이중체감법</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>오류_연수합계_잔존가치초과</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D134" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E134" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F134" t="n">
+        <v>5</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>연수합계법</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
